--- a/upload/Новинки за 2026 год первичка и вторичка.xlsx
+++ b/upload/Новинки за 2026 год первичка и вторичка.xlsx
@@ -463,19 +463,64 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="9" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="8" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -490,51 +535,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="9" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="8" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -545,6 +545,851 @@
     <cellStyle name="Обычный_Лист1" xfId="1"/>
   </cellStyles>
   <dxfs count="29">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="60"/>
+        </left>
+        <right style="thin">
+          <color indexed="60"/>
+        </right>
+        <top style="thin">
+          <color indexed="60"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="60"/>
+        </left>
+        <right style="thin">
+          <color indexed="60"/>
+        </right>
+        <top style="thin">
+          <color indexed="60"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="60"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="60"/>
+        </left>
+        <right style="thin">
+          <color indexed="60"/>
+        </right>
+        <top style="thin">
+          <color indexed="60"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="60"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="60"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="60"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="60"/>
+        </left>
+        <right style="thin">
+          <color indexed="60"/>
+        </right>
+        <top style="thin">
+          <color indexed="60"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="60"/>
+        </left>
+        <right style="thin">
+          <color indexed="60"/>
+        </right>
+        <top style="thin">
+          <color indexed="60"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="60"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="60"/>
+        </left>
+        <right style="thin">
+          <color indexed="60"/>
+        </right>
+        <top style="thin">
+          <color indexed="60"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="60"/>
+        </left>
+        <right style="thin">
+          <color indexed="60"/>
+        </right>
+        <top style="thin">
+          <color indexed="60"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="60"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="60"/>
+        </left>
+        <right style="thin">
+          <color indexed="60"/>
+        </right>
+        <top style="thin">
+          <color indexed="60"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="60"/>
+        </left>
+        <right style="thin">
+          <color indexed="60"/>
+        </right>
+        <top style="thin">
+          <color indexed="60"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="60"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="60"/>
+        </left>
+        <right style="thin">
+          <color indexed="60"/>
+        </right>
+        <top style="thin">
+          <color indexed="60"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="60"/>
+        </left>
+        <right style="thin">
+          <color indexed="60"/>
+        </right>
+        <top style="thin">
+          <color indexed="60"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="60"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="60"/>
+        </left>
+        <right style="thin">
+          <color indexed="60"/>
+        </right>
+        <top style="thin">
+          <color indexed="60"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="60"/>
+        </left>
+        <right style="thin">
+          <color indexed="60"/>
+        </right>
+        <top style="thin">
+          <color indexed="60"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="60"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="60"/>
+        </left>
+        <right style="thin">
+          <color indexed="60"/>
+        </right>
+        <top style="thin">
+          <color indexed="60"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="60"/>
+        </left>
+        <right style="thin">
+          <color indexed="60"/>
+        </right>
+        <top style="thin">
+          <color indexed="60"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="60"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="60"/>
+        </left>
+        <right style="thin">
+          <color indexed="60"/>
+        </right>
+        <top style="thin">
+          <color indexed="60"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="60"/>
+        </left>
+        <right style="thin">
+          <color indexed="60"/>
+        </right>
+        <top style="thin">
+          <color indexed="60"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="60"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="60"/>
+        </left>
+        <right style="thin">
+          <color indexed="60"/>
+        </right>
+        <top style="thin">
+          <color indexed="60"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="60"/>
+        </left>
+        <right style="thin">
+          <color indexed="60"/>
+        </right>
+        <top style="thin">
+          <color indexed="60"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="60"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="60"/>
+        </left>
+        <right style="thin">
+          <color indexed="60"/>
+        </right>
+        <top style="thin">
+          <color indexed="60"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="60"/>
+        </left>
+        <right style="thin">
+          <color indexed="60"/>
+        </right>
+        <top style="thin">
+          <color indexed="60"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="60"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -637,851 +1482,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="60"/>
-        </left>
-        <right style="thin">
-          <color indexed="60"/>
-        </right>
-        <top style="thin">
-          <color indexed="60"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="60"/>
-        </left>
-        <right style="thin">
-          <color indexed="60"/>
-        </right>
-        <top style="thin">
-          <color indexed="60"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="60"/>
-        </left>
-        <right style="thin">
-          <color indexed="60"/>
-        </right>
-        <top style="thin">
-          <color indexed="60"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="60"/>
-        </left>
-        <right style="thin">
-          <color indexed="60"/>
-        </right>
-        <top style="thin">
-          <color indexed="60"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="60"/>
-        </left>
-        <right style="thin">
-          <color indexed="60"/>
-        </right>
-        <top style="thin">
-          <color indexed="60"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="60"/>
-        </left>
-        <right style="thin">
-          <color indexed="60"/>
-        </right>
-        <top style="thin">
-          <color indexed="60"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="60"/>
-        </left>
-        <right style="thin">
-          <color indexed="60"/>
-        </right>
-        <top style="thin">
-          <color indexed="60"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="60"/>
-        </left>
-        <right style="thin">
-          <color indexed="60"/>
-        </right>
-        <top style="thin">
-          <color indexed="60"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="60"/>
-        </left>
-        <right style="thin">
-          <color indexed="60"/>
-        </right>
-        <top style="thin">
-          <color indexed="60"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="60"/>
-        </left>
-        <right style="thin">
-          <color indexed="60"/>
-        </right>
-        <top style="thin">
-          <color indexed="60"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="60"/>
-        </left>
-        <right style="thin">
-          <color indexed="60"/>
-        </right>
-        <top style="thin">
-          <color indexed="60"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="60"/>
-        </left>
-        <right style="thin">
-          <color indexed="60"/>
-        </right>
-        <top style="thin">
-          <color indexed="60"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="60"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="60"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="60"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="60"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="60"/>
-        </left>
-        <right style="thin">
-          <color indexed="60"/>
-        </right>
-        <top style="thin">
-          <color indexed="60"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="60"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="60"/>
-        </left>
-        <right style="thin">
-          <color indexed="60"/>
-        </right>
-        <top style="thin">
-          <color indexed="60"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="60"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="60"/>
-        </left>
-        <right style="thin">
-          <color indexed="60"/>
-        </right>
-        <top style="thin">
-          <color indexed="60"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="60"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="60"/>
-        </left>
-        <right style="thin">
-          <color indexed="60"/>
-        </right>
-        <top style="thin">
-          <color indexed="60"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="60"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="60"/>
-        </left>
-        <right style="thin">
-          <color indexed="60"/>
-        </right>
-        <top style="thin">
-          <color indexed="60"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="60"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="60"/>
-        </left>
-        <right style="thin">
-          <color indexed="60"/>
-        </right>
-        <top style="thin">
-          <color indexed="60"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="60"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="60"/>
-        </left>
-        <right style="thin">
-          <color indexed="60"/>
-        </right>
-        <top style="thin">
-          <color indexed="60"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="60"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="60"/>
-        </left>
-        <right style="thin">
-          <color indexed="60"/>
-        </right>
-        <top style="thin">
-          <color indexed="60"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="60"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="60"/>
-        </left>
-        <right style="thin">
-          <color indexed="60"/>
-        </right>
-        <top style="thin">
-          <color indexed="60"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="60"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border outline="0">
         <top style="thin">
           <color indexed="60"/>
@@ -1579,28 +1579,28 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Таблица3" displayName="Таблица3" ref="B2:M32" totalsRowCount="1" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24" headerRowCellStyle="Обычный_Лист1" dataCellStyle="Обычный_Лист1">
-  <autoFilter ref="B2:M32"/>
+  <autoFilter ref="B2:M31"/>
   <tableColumns count="12">
-    <tableColumn id="1" name="Период год" dataDxfId="1" totalsRowDxfId="0" dataCellStyle="Обычный_Лист1"/>
-    <tableColumn id="2" name="Серия торговой марки" dataDxfId="23" totalsRowDxfId="12" dataCellStyle="Обычный_Лист1"/>
-    <tableColumn id="3" name="Код" dataDxfId="22" totalsRowDxfId="11" dataCellStyle="Обычный_Лист1"/>
-    <tableColumn id="4" name="Номенклатура" dataDxfId="21" totalsRowDxfId="10" dataCellStyle="Обычный_Лист1"/>
-    <tableColumn id="5" name="Статус продукции" dataDxfId="20" totalsRowDxfId="9" dataCellStyle="Обычный_Лист1"/>
-    <tableColumn id="6" name="Вид продукции" dataDxfId="19" totalsRowDxfId="8" dataCellStyle="Обычный_Лист1"/>
-    <tableColumn id="7" name="Тип продукции" dataDxfId="18" totalsRowDxfId="7" dataCellStyle="Обычный_Лист1"/>
-    <tableColumn id="8" name="Первичка, кг" totalsRowFunction="custom" dataDxfId="17" totalsRowDxfId="6" dataCellStyle="Обычный_Лист1">
+    <tableColumn id="1" name="Период год" dataDxfId="23" totalsRowDxfId="22" dataCellStyle="Обычный_Лист1"/>
+    <tableColumn id="2" name="Серия торговой марки" dataDxfId="21" totalsRowDxfId="20" dataCellStyle="Обычный_Лист1"/>
+    <tableColumn id="3" name="Код" dataDxfId="19" totalsRowDxfId="18" dataCellStyle="Обычный_Лист1"/>
+    <tableColumn id="4" name="Номенклатура" dataDxfId="17" totalsRowDxfId="16" dataCellStyle="Обычный_Лист1"/>
+    <tableColumn id="5" name="Статус продукции" dataDxfId="15" totalsRowDxfId="14" dataCellStyle="Обычный_Лист1"/>
+    <tableColumn id="6" name="Вид продукции" dataDxfId="13" totalsRowDxfId="12" dataCellStyle="Обычный_Лист1"/>
+    <tableColumn id="7" name="Тип продукции" dataDxfId="11" totalsRowDxfId="10" dataCellStyle="Обычный_Лист1"/>
+    <tableColumn id="8" name="Первичка, кг" totalsRowFunction="custom" dataDxfId="9" totalsRowDxfId="8" dataCellStyle="Обычный_Лист1">
       <totalsRowFormula>SUM(I28:I31)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="9" name="Первичка, руб" totalsRowFunction="custom" dataDxfId="16" totalsRowDxfId="5" dataCellStyle="Обычный_Лист1">
+    <tableColumn id="9" name="Первичка, руб" totalsRowFunction="custom" dataDxfId="7" totalsRowDxfId="6" dataCellStyle="Обычный_Лист1">
       <totalsRowFormula>SUM(J28:J31)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="10" name="Вторичка, кг" totalsRowFunction="custom" dataDxfId="15" totalsRowDxfId="4" dataCellStyle="Обычный_Лист1">
+    <tableColumn id="10" name="Вторичка, кг" totalsRowFunction="custom" dataDxfId="5" totalsRowDxfId="4" dataCellStyle="Обычный_Лист1">
       <totalsRowFormula>SUM(K28:K31)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="11" name="Вторичка, руб" totalsRowFunction="custom" dataDxfId="14" totalsRowDxfId="3" dataCellStyle="Обычный_Лист1">
+    <tableColumn id="11" name="Вторичка, руб" totalsRowFunction="custom" dataDxfId="3" totalsRowDxfId="2" dataCellStyle="Обычный_Лист1">
       <totalsRowFormula>SUM(L28:L31)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="12" name="АКБ" totalsRowFunction="custom" dataDxfId="13" totalsRowDxfId="2" dataCellStyle="Обычный_Лист1">
+    <tableColumn id="12" name="АКБ" totalsRowFunction="custom" dataDxfId="1" totalsRowDxfId="0" dataCellStyle="Обычный_Лист1">
       <totalsRowFormula>SUM(M28:M31)</totalsRowFormula>
     </tableColumn>
   </tableColumns>
@@ -1897,7 +1897,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1952,7 +1952,7 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="36" t="s">
         <v>49</v>
       </c>
       <c r="B2" s="17" t="s">
@@ -1993,544 +1993,544 @@
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="18">
+      <c r="A3" s="37">
         <v>1</v>
       </c>
-      <c r="B3" s="28">
+      <c r="B3" s="22">
         <v>2026</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="30">
+      <c r="D3" s="24">
         <v>88845</v>
       </c>
-      <c r="E3" s="31" t="s">
+      <c r="E3" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F3" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="G3" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="31" t="s">
+      <c r="H3" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="32">
+      <c r="I3" s="26">
         <v>192</v>
       </c>
-      <c r="J3" s="33">
+      <c r="J3" s="27">
         <v>86925</v>
       </c>
-      <c r="K3" s="33">
+      <c r="K3" s="27">
         <v>21</v>
       </c>
-      <c r="L3" s="33">
+      <c r="L3" s="27">
         <v>12132.859999999999</v>
       </c>
-      <c r="M3" s="34">
+      <c r="M3" s="28">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="18"/>
-      <c r="B4" s="28">
+      <c r="A4" s="37"/>
+      <c r="B4" s="22">
         <v>2026</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="24">
         <v>88846</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="31" t="s">
+      <c r="F4" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="31" t="s">
+      <c r="G4" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="31" t="s">
+      <c r="H4" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="26">
         <v>132</v>
       </c>
-      <c r="J4" s="33">
+      <c r="J4" s="27">
         <v>53680</v>
       </c>
-      <c r="K4" s="33">
+      <c r="K4" s="27">
         <v>6</v>
       </c>
-      <c r="L4" s="33">
+      <c r="L4" s="27">
         <v>3082.94</v>
       </c>
-      <c r="M4" s="35">
+      <c r="M4" s="29">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
-      <c r="B5" s="28">
+      <c r="A5" s="37"/>
+      <c r="B5" s="22">
         <v>2026</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="24">
         <v>88847</v>
       </c>
-      <c r="E5" s="31" t="s">
+      <c r="E5" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="31" t="s">
+      <c r="F5" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="31" t="s">
+      <c r="G5" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="31" t="s">
+      <c r="H5" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="32">
+      <c r="I5" s="26">
         <v>194.4</v>
       </c>
-      <c r="J5" s="33">
+      <c r="J5" s="27">
         <v>97216.92</v>
       </c>
-      <c r="K5" s="33">
+      <c r="K5" s="27">
         <v>23.400000000000002</v>
       </c>
-      <c r="L5" s="33">
+      <c r="L5" s="27">
         <v>15156.73</v>
       </c>
-      <c r="M5" s="35">
+      <c r="M5" s="29">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="28">
+      <c r="A6" s="37"/>
+      <c r="B6" s="22">
         <v>2026</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="24">
         <v>88848</v>
       </c>
-      <c r="E6" s="31" t="s">
+      <c r="E6" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="F6" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="31" t="s">
+      <c r="G6" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="31" t="s">
+      <c r="H6" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="32">
+      <c r="I6" s="26">
         <v>118.8</v>
       </c>
-      <c r="J6" s="33">
+      <c r="J6" s="27">
         <v>53680</v>
       </c>
-      <c r="K6" s="33"/>
-      <c r="L6" s="33"/>
-      <c r="M6" s="35">
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="18"/>
-      <c r="B7" s="28">
+      <c r="A7" s="37"/>
+      <c r="B7" s="22">
         <v>2026</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="24">
         <v>88849</v>
       </c>
-      <c r="E7" s="31" t="s">
+      <c r="E7" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="31" t="s">
+      <c r="F7" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="31" t="s">
+      <c r="G7" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="31" t="s">
+      <c r="H7" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="32">
+      <c r="I7" s="26">
         <v>228</v>
       </c>
-      <c r="J7" s="33">
+      <c r="J7" s="27">
         <v>101945.64</v>
       </c>
-      <c r="K7" s="33">
+      <c r="K7" s="27">
         <v>38</v>
       </c>
-      <c r="L7" s="33">
+      <c r="L7" s="27">
         <v>21964.78</v>
       </c>
-      <c r="M7" s="35">
+      <c r="M7" s="29">
         <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="18"/>
-      <c r="B8" s="28">
+      <c r="A8" s="37"/>
+      <c r="B8" s="22">
         <v>2026</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="24">
         <v>88851</v>
       </c>
-      <c r="E8" s="31" t="s">
+      <c r="E8" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="31" t="s">
+      <c r="F8" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="31" t="s">
+      <c r="G8" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="31" t="s">
+      <c r="H8" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="I8" s="32">
+      <c r="I8" s="26">
         <v>132</v>
       </c>
-      <c r="J8" s="33">
+      <c r="J8" s="27">
         <v>53680</v>
       </c>
-      <c r="K8" s="33">
+      <c r="K8" s="27">
         <v>15</v>
       </c>
-      <c r="L8" s="33">
+      <c r="L8" s="27">
         <v>7950.74</v>
       </c>
-      <c r="M8" s="35">
+      <c r="M8" s="29">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="18"/>
-      <c r="B9" s="28">
+      <c r="A9" s="37"/>
+      <c r="B9" s="22">
         <v>2026</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="24">
         <v>88852</v>
       </c>
-      <c r="E9" s="31" t="s">
+      <c r="E9" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="31" t="s">
+      <c r="F9" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="31" t="s">
+      <c r="G9" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="31" t="s">
+      <c r="H9" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="32">
+      <c r="I9" s="26">
         <v>124.2</v>
       </c>
-      <c r="J9" s="33">
+      <c r="J9" s="27">
         <v>60221.64</v>
       </c>
-      <c r="K9" s="33">
+      <c r="K9" s="27">
         <v>29.700000000000003</v>
       </c>
-      <c r="L9" s="33">
+      <c r="L9" s="27">
         <v>19080.47</v>
       </c>
-      <c r="M9" s="35">
+      <c r="M9" s="29">
         <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="18"/>
-      <c r="B10" s="28">
+      <c r="A10" s="37"/>
+      <c r="B10" s="22">
         <v>2026</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="24">
         <v>88853</v>
       </c>
-      <c r="E10" s="31" t="s">
+      <c r="E10" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="31" t="s">
+      <c r="F10" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="31" t="s">
+      <c r="G10" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="31" t="s">
+      <c r="H10" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="I10" s="32">
+      <c r="I10" s="26">
         <v>108</v>
       </c>
-      <c r="J10" s="33">
+      <c r="J10" s="27">
         <v>48800</v>
       </c>
-      <c r="K10" s="33">
+      <c r="K10" s="27">
         <v>8.1</v>
       </c>
-      <c r="L10" s="33">
+      <c r="L10" s="27">
         <v>4867.8</v>
       </c>
-      <c r="M10" s="35">
+      <c r="M10" s="29">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
-      <c r="B11" s="28">
+      <c r="A11" s="37"/>
+      <c r="B11" s="22">
         <v>2026</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="24">
         <v>88854</v>
       </c>
-      <c r="E11" s="31" t="s">
+      <c r="E11" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="F11" s="31" t="s">
+      <c r="F11" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="31" t="s">
+      <c r="G11" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="31" t="s">
+      <c r="H11" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="I11" s="32">
+      <c r="I11" s="26">
         <v>113.4</v>
       </c>
-      <c r="J11" s="33">
+      <c r="J11" s="27">
         <v>54958.41</v>
       </c>
-      <c r="K11" s="33">
+      <c r="K11" s="27">
         <v>23.400000000000002</v>
       </c>
-      <c r="L11" s="33">
+      <c r="L11" s="27">
         <v>15030.2</v>
       </c>
-      <c r="M11" s="35">
+      <c r="M11" s="29">
         <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="18"/>
-      <c r="B12" s="28">
+      <c r="A12" s="37"/>
+      <c r="B12" s="22">
         <v>2026</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="24">
         <v>88855</v>
       </c>
-      <c r="E12" s="31" t="s">
+      <c r="E12" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="31" t="s">
+      <c r="F12" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G12" s="31" t="s">
+      <c r="G12" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="31" t="s">
+      <c r="H12" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="I12" s="32">
+      <c r="I12" s="26">
         <v>108</v>
       </c>
-      <c r="J12" s="33">
+      <c r="J12" s="27">
         <v>48800</v>
       </c>
-      <c r="K12" s="33">
+      <c r="K12" s="27">
         <v>5.4</v>
       </c>
-      <c r="L12" s="33">
+      <c r="L12" s="27">
         <v>3082.94</v>
       </c>
-      <c r="M12" s="35">
+      <c r="M12" s="29">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="18"/>
-      <c r="B13" s="28">
+      <c r="A13" s="37"/>
+      <c r="B13" s="22">
         <v>2026</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="24">
         <v>88856</v>
       </c>
-      <c r="E13" s="31" t="s">
+      <c r="E13" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="31" t="s">
+      <c r="F13" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G13" s="31" t="s">
+      <c r="G13" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="H13" s="31" t="s">
+      <c r="H13" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="I13" s="32">
+      <c r="I13" s="26">
         <v>180</v>
       </c>
-      <c r="J13" s="33">
+      <c r="J13" s="27">
         <v>82196.28</v>
       </c>
-      <c r="K13" s="33">
+      <c r="K13" s="27">
         <v>8</v>
       </c>
-      <c r="L13" s="33">
+      <c r="L13" s="27">
         <v>4649.16</v>
       </c>
-      <c r="M13" s="35">
+      <c r="M13" s="29">
         <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="18"/>
-      <c r="B14" s="28">
+      <c r="A14" s="37"/>
+      <c r="B14" s="22">
         <v>2026</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="24">
         <v>88857</v>
       </c>
-      <c r="E14" s="31" t="s">
+      <c r="E14" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="31" t="s">
+      <c r="F14" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G14" s="31" t="s">
+      <c r="G14" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="31" t="s">
+      <c r="H14" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="I14" s="32">
+      <c r="I14" s="26">
         <v>41.6</v>
       </c>
-      <c r="J14" s="33">
+      <c r="J14" s="27">
         <v>17885.830000000002</v>
       </c>
-      <c r="K14" s="33">
+      <c r="K14" s="27">
         <v>15.6</v>
       </c>
-      <c r="L14" s="33">
+      <c r="L14" s="27">
         <v>8664.6</v>
       </c>
-      <c r="M14" s="35">
+      <c r="M14" s="29">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="18"/>
-      <c r="B15" s="28">
+      <c r="A15" s="37"/>
+      <c r="B15" s="22">
         <v>2026</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="24">
         <v>88858</v>
       </c>
-      <c r="E15" s="31" t="s">
+      <c r="E15" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="F15" s="31" t="s">
+      <c r="F15" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G15" s="31" t="s">
+      <c r="G15" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="31" t="s">
+      <c r="H15" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="I15" s="32">
+      <c r="I15" s="26">
         <v>37.799999999999997</v>
       </c>
-      <c r="J15" s="33">
+      <c r="J15" s="27">
         <v>16797.57</v>
       </c>
-      <c r="K15" s="33"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="35">
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="18"/>
-      <c r="B16" s="28">
+      <c r="A16" s="37"/>
+      <c r="B16" s="22">
         <v>2026</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="24">
         <v>88859</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="E16" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F16" s="31" t="s">
+      <c r="F16" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G16" s="31" t="s">
+      <c r="G16" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="H16" s="31" t="s">
+      <c r="H16" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="I16" s="32">
+      <c r="I16" s="26">
         <v>64.400000000000006</v>
       </c>
-      <c r="J16" s="33">
+      <c r="J16" s="27">
         <v>27328</v>
       </c>
-      <c r="K16" s="33"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="35">
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="16"/>
-      <c r="B17" s="19"/>
+      <c r="B17" s="18"/>
       <c r="C17" s="13"/>
       <c r="D17" s="11"/>
       <c r="E17" s="12"/>
@@ -2559,127 +2559,127 @@
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="18">
+      <c r="A18" s="37">
         <v>2</v>
       </c>
-      <c r="B18" s="28">
+      <c r="B18" s="22">
         <v>2026</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="24">
         <v>88965</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="E18" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="F18" s="31" t="s">
+      <c r="F18" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G18" s="31" t="s">
+      <c r="G18" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="H18" s="31" t="s">
+      <c r="H18" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="I18" s="32">
+      <c r="I18" s="26">
         <v>1566</v>
       </c>
-      <c r="J18" s="33">
+      <c r="J18" s="27">
         <v>371366.02</v>
       </c>
-      <c r="K18" s="33">
+      <c r="K18" s="27">
         <v>596</v>
       </c>
-      <c r="L18" s="33">
+      <c r="L18" s="27">
         <v>164256.75</v>
       </c>
-      <c r="M18" s="35">
+      <c r="M18" s="29">
         <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="18"/>
-      <c r="B19" s="28">
+      <c r="A19" s="37"/>
+      <c r="B19" s="22">
         <v>2026</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="24">
         <v>88966</v>
       </c>
-      <c r="E19" s="31" t="s">
+      <c r="E19" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="F19" s="31" t="s">
+      <c r="F19" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G19" s="31" t="s">
+      <c r="G19" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="H19" s="31" t="s">
+      <c r="H19" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="I19" s="32">
+      <c r="I19" s="26">
         <v>4344</v>
       </c>
-      <c r="J19" s="33">
+      <c r="J19" s="27">
         <v>897330.48</v>
       </c>
-      <c r="K19" s="33">
+      <c r="K19" s="27">
         <v>1182</v>
       </c>
-      <c r="L19" s="33">
+      <c r="L19" s="27">
         <v>263486.67</v>
       </c>
-      <c r="M19" s="35">
+      <c r="M19" s="29">
         <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="18"/>
-      <c r="B20" s="28">
+      <c r="A20" s="37"/>
+      <c r="B20" s="22">
         <v>2026</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="24">
         <v>88967</v>
       </c>
-      <c r="E20" s="31" t="s">
+      <c r="E20" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="F20" s="31" t="s">
+      <c r="F20" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G20" s="31" t="s">
+      <c r="G20" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="H20" s="31" t="s">
+      <c r="H20" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="I20" s="32">
+      <c r="I20" s="26">
         <v>1836</v>
       </c>
-      <c r="J20" s="33">
+      <c r="J20" s="27">
         <v>346858.93</v>
       </c>
-      <c r="K20" s="33">
+      <c r="K20" s="27">
         <v>216</v>
       </c>
-      <c r="L20" s="33">
+      <c r="L20" s="27">
         <v>48655.8</v>
       </c>
-      <c r="M20" s="35">
+      <c r="M20" s="29">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="22"/>
-      <c r="B21" s="20"/>
+      <c r="A21" s="21"/>
+      <c r="B21" s="19"/>
       <c r="C21" s="14"/>
       <c r="D21" s="8"/>
       <c r="E21" s="7"/>
@@ -2708,80 +2708,80 @@
       </c>
     </row>
     <row r="22" spans="1:13" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="18">
+      <c r="A22" s="37">
         <v>3</v>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="22">
         <v>2026</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="24">
         <v>89507</v>
       </c>
-      <c r="E22" s="31" t="s">
+      <c r="E22" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="F22" s="31" t="s">
+      <c r="F22" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G22" s="31" t="s">
+      <c r="G22" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="H22" s="31" t="s">
+      <c r="H22" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="I22" s="32">
+      <c r="I22" s="26">
         <v>95.2</v>
       </c>
-      <c r="J22" s="33">
+      <c r="J22" s="27">
         <v>17177.21</v>
       </c>
-      <c r="K22" s="33"/>
-      <c r="L22" s="33"/>
-      <c r="M22" s="35">
+      <c r="K22" s="27"/>
+      <c r="L22" s="27"/>
+      <c r="M22" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="18"/>
-      <c r="B23" s="28">
+      <c r="A23" s="37"/>
+      <c r="B23" s="22">
         <v>2026</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="30">
+      <c r="D23" s="24">
         <v>89508</v>
       </c>
-      <c r="E23" s="31" t="s">
+      <c r="E23" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="F23" s="31" t="s">
+      <c r="F23" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G23" s="31" t="s">
+      <c r="G23" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="H23" s="31" t="s">
+      <c r="H23" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="I23" s="32">
+      <c r="I23" s="26">
         <v>597.70000000000005</v>
       </c>
-      <c r="J23" s="33">
+      <c r="J23" s="27">
         <v>93831.59</v>
       </c>
-      <c r="K23" s="33"/>
-      <c r="L23" s="33"/>
-      <c r="M23" s="35">
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="22"/>
-      <c r="B24" s="20"/>
+      <c r="A24" s="21"/>
+      <c r="B24" s="19"/>
       <c r="C24" s="14"/>
       <c r="D24" s="8"/>
       <c r="E24" s="7"/>
@@ -2810,80 +2810,80 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="23">
+      <c r="A25" s="38">
         <v>4</v>
       </c>
-      <c r="B25" s="28">
+      <c r="B25" s="22">
         <v>2026</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D25" s="24">
         <v>63627</v>
       </c>
-      <c r="E25" s="31" t="s">
+      <c r="E25" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="F25" s="31" t="s">
+      <c r="F25" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G25" s="31" t="s">
+      <c r="G25" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="H25" s="31" t="s">
+      <c r="H25" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="I25" s="32">
+      <c r="I25" s="26">
         <v>48</v>
       </c>
-      <c r="J25" s="33">
+      <c r="J25" s="27">
         <v>12663.6</v>
       </c>
-      <c r="K25" s="33"/>
-      <c r="L25" s="33"/>
-      <c r="M25" s="35">
+      <c r="K25" s="27"/>
+      <c r="L25" s="27"/>
+      <c r="M25" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="24"/>
-      <c r="B26" s="28">
+      <c r="A26" s="39"/>
+      <c r="B26" s="22">
         <v>2026</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C26" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D26" s="30">
+      <c r="D26" s="24">
         <v>89357</v>
       </c>
-      <c r="E26" s="31" t="s">
+      <c r="E26" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="F26" s="31" t="s">
+      <c r="F26" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G26" s="31" t="s">
+      <c r="G26" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="H26" s="31" t="s">
+      <c r="H26" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="I26" s="32">
+      <c r="I26" s="26">
         <v>188.5</v>
       </c>
-      <c r="J26" s="33">
+      <c r="J26" s="27">
         <v>44725.2</v>
       </c>
-      <c r="K26" s="33"/>
-      <c r="L26" s="33"/>
-      <c r="M26" s="35">
+      <c r="K26" s="27"/>
+      <c r="L26" s="27"/>
+      <c r="M26" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="22"/>
-      <c r="B27" s="20"/>
+      <c r="A27" s="21"/>
+      <c r="B27" s="19"/>
       <c r="C27" s="14"/>
       <c r="D27" s="8"/>
       <c r="E27" s="7"/>
@@ -2912,162 +2912,162 @@
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="25">
+      <c r="A28" s="40">
         <v>5</v>
       </c>
-      <c r="B28" s="28">
+      <c r="B28" s="22">
         <v>2026</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D28" s="30">
+      <c r="D28" s="24">
         <v>89855</v>
       </c>
-      <c r="E28" s="31" t="s">
+      <c r="E28" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="F28" s="31" t="s">
+      <c r="F28" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G28" s="31" t="s">
+      <c r="G28" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="H28" s="31" t="s">
+      <c r="H28" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="I28" s="32">
+      <c r="I28" s="26">
         <v>592.79999999999995</v>
       </c>
-      <c r="J28" s="33">
+      <c r="J28" s="27">
         <v>184244.4</v>
       </c>
-      <c r="K28" s="33">
+      <c r="K28" s="27">
         <v>28.599999999999998</v>
       </c>
-      <c r="L28" s="33">
+      <c r="L28" s="27">
         <v>11728.8</v>
       </c>
-      <c r="M28" s="35">
+      <c r="M28" s="29">
         <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="26"/>
-      <c r="B29" s="28">
+      <c r="A29" s="41"/>
+      <c r="B29" s="22">
         <v>2026</v>
       </c>
-      <c r="C29" s="29" t="s">
+      <c r="C29" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D29" s="30">
+      <c r="D29" s="24">
         <v>89856</v>
       </c>
-      <c r="E29" s="31" t="s">
+      <c r="E29" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="F29" s="31" t="s">
+      <c r="F29" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G29" s="31" t="s">
+      <c r="G29" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="H29" s="31" t="s">
+      <c r="H29" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="I29" s="32">
+      <c r="I29" s="26">
         <v>1908</v>
       </c>
-      <c r="J29" s="33">
+      <c r="J29" s="27">
         <v>460947</v>
       </c>
-      <c r="K29" s="33">
+      <c r="K29" s="27">
         <v>36</v>
       </c>
-      <c r="L29" s="33">
+      <c r="L29" s="27">
         <v>12738</v>
       </c>
-      <c r="M29" s="35">
+      <c r="M29" s="29">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="26"/>
-      <c r="B30" s="28">
+      <c r="A30" s="41"/>
+      <c r="B30" s="22">
         <v>2026</v>
       </c>
-      <c r="C30" s="29" t="s">
+      <c r="C30" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D30" s="30">
+      <c r="D30" s="24">
         <v>89857</v>
       </c>
-      <c r="E30" s="31" t="s">
+      <c r="E30" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="F30" s="31" t="s">
+      <c r="F30" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G30" s="31" t="s">
+      <c r="G30" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="H30" s="31" t="s">
+      <c r="H30" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="I30" s="32">
+      <c r="I30" s="26">
         <v>1092</v>
       </c>
-      <c r="J30" s="33">
+      <c r="J30" s="27">
         <v>243778.08</v>
       </c>
-      <c r="K30" s="33">
+      <c r="K30" s="27">
         <v>6</v>
       </c>
-      <c r="L30" s="33">
+      <c r="L30" s="27">
         <v>1617.33</v>
       </c>
-      <c r="M30" s="35">
+      <c r="M30" s="29">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="27"/>
-      <c r="B31" s="28">
+      <c r="A31" s="42"/>
+      <c r="B31" s="22">
         <v>2026</v>
       </c>
-      <c r="C31" s="36" t="s">
+      <c r="C31" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="37">
+      <c r="D31" s="31">
         <v>89858</v>
       </c>
-      <c r="E31" s="38" t="s">
+      <c r="E31" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="F31" s="38" t="s">
+      <c r="F31" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="G31" s="38" t="s">
+      <c r="G31" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="H31" s="38" t="s">
+      <c r="H31" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="I31" s="39">
+      <c r="I31" s="33">
         <v>684</v>
       </c>
-      <c r="J31" s="40">
+      <c r="J31" s="34">
         <v>169433.04</v>
       </c>
-      <c r="K31" s="33"/>
-      <c r="L31" s="33"/>
-      <c r="M31" s="41">
+      <c r="K31" s="27"/>
+      <c r="L31" s="27"/>
+      <c r="M31" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="16"/>
-      <c r="B32" s="21"/>
+      <c r="B32" s="20"/>
       <c r="C32" s="15"/>
       <c r="D32" s="10"/>
       <c r="E32" s="9"/>
@@ -3097,12 +3097,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A1:C1"/>
     <mergeCell ref="A3:A16"/>
     <mergeCell ref="A18:A20"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="A28:A31"/>
-    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
